--- a/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
@@ -1255,7 +1255,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common)
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
@@ -627,16 +627,16 @@
     <t>FiveWs.class</t>
   </si>
   <si>
-    <t>Observation.category:socialHistory</t>
-  </si>
-  <si>
-    <t>socialHistory</t>
+    <t>Observation.category:first</t>
+  </si>
+  <si>
+    <t>first</t>
   </si>
   <si>
     <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
-    <t>Observation.category:socialHistory.id</t>
+    <t>Observation.category:first.id</t>
   </si>
   <si>
     <t>Observation.category.id</t>
@@ -658,7 +658,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>Observation.category:socialHistory.extension</t>
+    <t>Observation.category:first.extension</t>
   </si>
   <si>
     <t>Observation.category.extension</t>
@@ -677,7 +677,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>Observation.category:socialHistory.coding</t>
+    <t>Observation.category:first.coding</t>
   </si>
   <si>
     <t>Observation.category.coding</t>
@@ -708,19 +708,19 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
-    <t>Observation.category:socialHistory.coding.id</t>
+    <t>Observation.category:first.coding.id</t>
   </si>
   <si>
     <t>Observation.category.coding.id</t>
   </si>
   <si>
-    <t>Observation.category:socialHistory.coding.extension</t>
+    <t>Observation.category:first.coding.extension</t>
   </si>
   <si>
     <t>Observation.category.coding.extension</t>
   </si>
   <si>
-    <t>Observation.category:socialHistory.coding.system</t>
+    <t>Observation.category:first.coding.system</t>
   </si>
   <si>
     <t>Observation.category.coding.system</t>
@@ -750,7 +750,7 @@
     <t>./codeSystem</t>
   </si>
   <si>
-    <t>Observation.category:socialHistory.coding.version</t>
+    <t>Observation.category:first.coding.version</t>
   </si>
   <si>
     <t>Observation.category.coding.version</t>
@@ -774,7 +774,7 @@
     <t>./codeSystemVersion</t>
   </si>
   <si>
-    <t>Observation.category:socialHistory.coding.code</t>
+    <t>Observation.category:first.coding.code</t>
   </si>
   <si>
     <t>Observation.category.coding.code</t>
@@ -801,7 +801,7 @@
     <t>./code</t>
   </si>
   <si>
-    <t>Observation.category:socialHistory.coding.display</t>
+    <t>Observation.category:first.coding.display</t>
   </si>
   <si>
     <t>Observation.category.coding.display</t>
@@ -825,7 +825,7 @@
     <t>CV.displayName</t>
   </si>
   <si>
-    <t>Observation.category:socialHistory.coding.userSelected</t>
+    <t>Observation.category:first.coding.userSelected</t>
   </si>
   <si>
     <t>Observation.category.coding.userSelected</t>
@@ -856,7 +856,7 @@
     <t>CD.codingRationale</t>
   </si>
   <si>
-    <t>Observation.category:socialHistory.text</t>
+    <t>Observation.category:first.text</t>
   </si>
   <si>
     <t>Observation.category.text</t>
@@ -1923,9 +1923,9 @@
   <dimension ref="A1:AP63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.5" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.79296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
@@ -279,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -326,16 +326,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -461,7 +461,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -1318,7 +1318,7 @@
     <t>どの値が「正常」と見なされるかを知ることは、特定の結果の意義を評価するのに役立つ。さまざまなコンテキストに対応するため複数の参照範囲を提供できる必要がある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2454" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2455" uniqueCount="516">
   <si>
     <t>Property</t>
   </si>
@@ -611,29 +611,41 @@
     <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
+    <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:coding.system}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:first</t>
+  </si>
+  <si>
+    <t>first</t>
+  </si>
+  <si>
+    <t>検査の第1カテゴリはJP_SimpleObservationCategory_VSから値を指定する。</t>
+  </si>
+  <si>
+    <t>行われている一般的なタイプの観測を分類するコード。 / A code that classifies the general type of observation being made.</t>
+  </si>
+  <si>
+    <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:$this}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:first</t>
-  </si>
-  <si>
-    <t>first</t>
-  </si>
-  <si>
-    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
     <t>Observation.category:first.id</t>
@@ -3723,22 +3735,24 @@
       <c r="X15" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="Y15" s="2"/>
+      <c r="Y15" t="s" s="2">
+        <v>191</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>186</v>
@@ -3765,10 +3779,10 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -3776,13 +3790,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>186</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>83</v>
@@ -3792,7 +3806,7 @@
         <v>93</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>83</v>
@@ -3807,13 +3821,13 @@
         <v>187</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="O16" t="s" s="2">
         <v>190</v>
@@ -3845,7 +3859,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -3887,10 +3901,10 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>83</v>
@@ -3898,10 +3912,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3924,13 +3938,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3981,7 +3995,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4005,7 +4019,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4016,10 +4030,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4048,7 +4062,7 @@
         <v>140</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>142</v>
@@ -4089,19 +4103,19 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4125,7 +4139,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4136,10 +4150,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4162,19 +4176,19 @@
         <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4223,7 +4237,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4244,10 +4258,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4258,10 +4272,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4284,13 +4298,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4341,7 +4355,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4365,7 +4379,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4376,10 +4390,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4408,7 +4422,7 @@
         <v>140</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>142</v>
@@ -4449,19 +4463,19 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4485,7 +4499,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4496,10 +4510,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4507,7 +4521,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>93</v>
@@ -4525,23 +4539,23 @@
         <v>107</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4583,7 +4597,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4604,10 +4618,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4618,10 +4632,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4644,16 +4658,16 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4703,7 +4717,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4724,10 +4738,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4738,10 +4752,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4767,21 +4781,21 @@
         <v>113</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -4823,7 +4837,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4844,10 +4858,10 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -4858,10 +4872,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4884,17 +4898,17 @@
         <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -4943,7 +4957,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4964,10 +4978,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -4978,10 +4992,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5004,19 +5018,19 @@
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5065,7 +5079,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5086,10 +5100,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5100,10 +5114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5126,19 +5140,19 @@
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5187,7 +5201,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5208,10 +5222,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5222,14 +5236,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5251,16 +5265,16 @@
         <v>187</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5289,7 +5303,7 @@
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5307,7 +5321,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>93</v>
@@ -5322,30 +5336,30 @@
         <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5368,19 +5382,19 @@
         <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -5429,7 +5443,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5444,19 +5458,19 @@
         <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>83</v>
@@ -5464,10 +5478,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5490,16 +5504,16 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5549,7 +5563,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5570,13 +5584,13 @@
         <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>83</v>
@@ -5584,14 +5598,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5610,19 +5624,19 @@
         <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5671,7 +5685,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5686,19 +5700,19 @@
         <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>83</v>
@@ -5706,14 +5720,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5732,19 +5746,19 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>83</v>
@@ -5793,7 +5807,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5808,19 +5822,19 @@
         <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>83</v>
@@ -5828,10 +5842,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5854,16 +5868,16 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5913,7 +5927,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5934,13 +5948,13 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>83</v>
@@ -5948,10 +5962,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5974,19 +5988,19 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -6035,7 +6049,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6050,19 +6064,19 @@
         <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>83</v>
@@ -6070,10 +6084,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6096,19 +6110,19 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -6157,7 +6171,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6166,7 +6180,7 @@
         <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>105</v>
@@ -6175,27 +6189,27 @@
         <v>83</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6221,16 +6235,16 @@
         <v>187</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6255,31 +6269,31 @@
         <v>83</v>
       </c>
       <c r="X36" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6288,7 +6302,7 @@
         <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>105</v>
@@ -6303,7 +6317,7 @@
         <v>136</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6314,14 +6328,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6343,16 +6357,16 @@
         <v>187</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6377,13 +6391,13 @@
         <v>83</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -6401,7 +6415,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6419,27 +6433,27 @@
         <v>83</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6462,19 +6476,19 @@
         <v>83</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6523,7 +6537,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6544,10 +6558,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6558,10 +6572,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6587,13 +6601,13 @@
         <v>187</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6619,31 +6633,31 @@
         <v>83</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6661,27 +6675,27 @@
         <v>83</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6707,16 +6721,16 @@
         <v>187</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6741,31 +6755,31 @@
         <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6786,10 +6800,10 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
@@ -6800,10 +6814,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6826,16 +6840,16 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6885,7 +6899,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6903,27 +6917,27 @@
         <v>83</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6946,16 +6960,16 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7005,7 +7019,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7023,27 +7037,27 @@
         <v>83</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7066,19 +7080,19 @@
         <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7127,7 +7141,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7139,7 +7153,7 @@
         <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>83</v>
@@ -7148,10 +7162,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7162,10 +7176,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7188,13 +7202,13 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7245,7 +7259,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7269,7 +7283,7 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7280,10 +7294,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7312,7 +7326,7 @@
         <v>140</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>142</v>
@@ -7365,7 +7379,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7389,7 +7403,7 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7400,14 +7414,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7429,10 +7443,10 @@
         <v>139</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>142</v>
@@ -7487,7 +7501,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7522,10 +7536,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7548,13 +7562,13 @@
         <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7605,7 +7619,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7614,7 +7628,7 @@
         <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>105</v>
@@ -7626,10 +7640,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7640,10 +7654,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7666,13 +7680,13 @@
         <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7723,7 +7737,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7732,7 +7746,7 @@
         <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>105</v>
@@ -7744,10 +7758,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7758,10 +7772,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7787,16 +7801,16 @@
         <v>187</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7824,10 +7838,10 @@
         <v>117</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -7845,7 +7859,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7863,13 +7877,13 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -7880,10 +7894,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7909,16 +7923,16 @@
         <v>187</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -7943,13 +7957,13 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -7967,7 +7981,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7985,13 +7999,13 @@
         <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8002,10 +8016,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8028,17 +8042,17 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8087,7 +8101,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8111,7 +8125,7 @@
         <v>83</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8122,10 +8136,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8148,13 +8162,13 @@
         <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8205,7 +8219,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8226,10 +8240,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8240,10 +8254,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8266,16 +8280,16 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8325,7 +8339,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8346,10 +8360,10 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8360,10 +8374,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8386,16 +8400,16 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8445,7 +8459,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8466,10 +8480,10 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8480,10 +8494,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8506,19 +8520,19 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8567,7 +8581,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8588,10 +8602,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8602,10 +8616,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8628,13 +8642,13 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8685,7 +8699,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8709,7 +8723,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8720,10 +8734,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8752,7 +8766,7 @@
         <v>140</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>142</v>
@@ -8805,7 +8819,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8829,7 +8843,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -8840,14 +8854,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8869,10 +8883,10 @@
         <v>139</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>142</v>
@@ -8927,7 +8941,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8962,10 +8976,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8991,16 +9005,16 @@
         <v>187</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9025,31 +9039,31 @@
         <v>83</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>93</v>
@@ -9067,16 +9081,16 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>83</v>
@@ -9084,10 +9098,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9110,19 +9124,19 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9171,7 +9185,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9189,27 +9203,27 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9235,16 +9249,16 @@
         <v>187</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9269,13 +9283,13 @@
         <v>83</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
@@ -9293,7 +9307,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9302,7 +9316,7 @@
         <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>105</v>
@@ -9317,7 +9331,7 @@
         <v>136</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9328,14 +9342,14 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9357,16 +9371,16 @@
         <v>187</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9391,13 +9405,13 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9415,7 +9429,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9433,27 +9447,27 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9479,16 +9493,16 @@
         <v>84</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9537,7 +9551,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9558,10 +9572,10 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2455" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2454" uniqueCount="515">
   <si>
     <t>Property</t>
   </si>
@@ -1222,10 +1222,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -6635,11 +6632,9 @@
       <c r="X39" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="Y39" t="s" s="2">
+      <c r="Y39" s="2"/>
+      <c r="Z39" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -6675,27 +6670,27 @@
         <v>83</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP39" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>392</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6721,16 +6716,16 @@
         <v>187</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M40" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6758,11 +6753,11 @@
         <v>386</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>398</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
       </c>
@@ -6779,7 +6774,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6800,10 +6795,10 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
@@ -6814,10 +6809,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6840,16 +6835,16 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6899,7 +6894,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6917,27 +6912,27 @@
         <v>83</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP41" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>408</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6960,16 +6955,16 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7019,7 +7014,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7037,27 +7032,27 @@
         <v>83</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AO42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP42" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>416</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7080,19 +7075,19 @@
         <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="M43" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7141,7 +7136,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7153,19 +7148,19 @@
         <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AK43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7176,10 +7171,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7294,10 +7289,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7414,14 +7409,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7443,10 +7438,10 @@
         <v>139</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>142</v>
@@ -7501,7 +7496,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7536,10 +7531,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7562,13 +7557,13 @@
         <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7619,7 +7614,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7628,7 +7623,7 @@
         <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>105</v>
@@ -7640,10 +7635,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7654,10 +7649,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7680,13 +7675,13 @@
         <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7737,7 +7732,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7746,7 +7741,7 @@
         <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>105</v>
@@ -7758,10 +7753,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7772,10 +7767,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7801,16 +7796,16 @@
         <v>187</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7838,11 +7833,11 @@
         <v>117</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="Z49" t="s" s="2">
-        <v>449</v>
-      </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
       </c>
@@ -7859,7 +7854,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7877,10 +7872,10 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>374</v>
@@ -7894,10 +7889,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7923,16 +7918,16 @@
         <v>187</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -7960,11 +7955,11 @@
         <v>386</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>458</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
       </c>
@@ -7981,7 +7976,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7999,10 +7994,10 @@
         <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>374</v>
@@ -8016,10 +8011,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8042,17 +8037,17 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8101,7 +8096,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8125,7 +8120,7 @@
         <v>83</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8136,10 +8131,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8165,10 +8160,10 @@
         <v>205</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8219,7 +8214,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8240,10 +8235,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8254,10 +8249,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8280,16 +8275,16 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8339,7 +8334,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8360,10 +8355,10 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8374,10 +8369,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8400,16 +8395,16 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8459,7 +8454,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8480,10 +8475,10 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8494,10 +8489,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8520,19 +8515,19 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8581,7 +8576,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8602,10 +8597,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8616,10 +8611,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8734,10 +8729,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8854,14 +8849,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8883,10 +8878,10 @@
         <v>139</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>142</v>
@@ -8941,7 +8936,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8976,10 +8971,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9005,13 +9000,13 @@
         <v>187</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="O59" t="s" s="2">
         <v>288</v>
@@ -9042,11 +9037,11 @@
         <v>386</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="Z59" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>494</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>83</v>
       </c>
@@ -9063,7 +9058,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>93</v>
@@ -9081,7 +9076,7 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>292</v>
@@ -9098,10 +9093,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9124,16 +9119,16 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="O60" t="s" s="2">
         <v>350</v>
@@ -9185,7 +9180,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9203,7 +9198,7 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>353</v>
@@ -9220,10 +9215,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9249,13 +9244,13 @@
         <v>187</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>359</v>
@@ -9307,7 +9302,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9342,10 +9337,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9371,16 +9366,16 @@
         <v>187</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9429,7 +9424,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9464,10 +9459,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9493,16 +9488,16 @@
         <v>84</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9551,7 +9546,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9572,10 +9567,10 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
@@ -279,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReasonは、Observation.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:Observation.codeがObservation.component.codeと同じ場合、そのcodeに関連付くvalueは存在してはならない。 / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1138,7 +1138,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>結果（ `balue.value [x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
+    <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
@@ -1328,7 +1328,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
+obs-3:少なくともlow, high, textのいずれかが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
     <t>OBX.7</t>
@@ -1594,7 +1594,7 @@
   </si>
   <si>
     <t>「null」または例外的な値は、FHIR観測で2つの方法を表すことができます。1つの方法は、それらを単に値セットに含めるだけで、値の例外を表すことです。たとえば、血清学テストの測定値は、「検出」、「検出されない」、「決定的でない」、または「テストなし」です。
-別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、DataBsentrasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
+別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、dataAbsentReasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
 The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
   </si>
   <si>
@@ -1956,7 +1956,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="105.8828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="65.11328125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
@@ -1399,7 +1399,7 @@
     <t>Observation.referenceRange.type</t>
   </si>
   <si>
-    <t>参照範囲予選 / Reference range qualifier</t>
+    <t>参照範囲予選修飾子 / Reference range qualifier</t>
   </si>
   <si>
     <t>適用されるターゲット参照母集団のどの部分を示すコード。たとえば、通常または治療範囲。 / Codes to indicate the what part of the targeted reference population it applies to. For example, the normal or therapeutic range.</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
@@ -1932,15 +1932,15 @@
   <dimension ref="A1:AP63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1951,28 +1951,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="65.11328125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.48828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="55.82421875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2454" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2455" uniqueCount="516">
   <si>
     <t>Property</t>
   </si>
@@ -1222,7 +1222,10 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
+    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -6632,9 +6635,11 @@
       <c r="X39" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="Y39" s="2"/>
+      <c r="Y39" t="s" s="2">
+        <v>387</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -6670,27 +6675,27 @@
         <v>83</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6716,16 +6721,16 @@
         <v>187</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6753,10 +6758,10 @@
         <v>386</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6774,7 +6779,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6795,10 +6800,10 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
@@ -6809,10 +6814,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6835,16 +6840,16 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6894,7 +6899,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6912,27 +6917,27 @@
         <v>83</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6955,16 +6960,16 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7014,7 +7019,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7032,27 +7037,27 @@
         <v>83</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7075,19 +7080,19 @@
         <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7136,7 +7141,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7148,7 +7153,7 @@
         <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>83</v>
@@ -7157,10 +7162,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7171,10 +7176,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7289,10 +7294,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7409,14 +7414,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7438,10 +7443,10 @@
         <v>139</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>142</v>
@@ -7496,7 +7501,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7531,10 +7536,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7557,13 +7562,13 @@
         <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7614,7 +7619,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7623,7 +7628,7 @@
         <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>105</v>
@@ -7635,10 +7640,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7649,10 +7654,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7675,13 +7680,13 @@
         <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7732,7 +7737,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7741,7 +7746,7 @@
         <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>105</v>
@@ -7753,10 +7758,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7767,10 +7772,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7796,16 +7801,16 @@
         <v>187</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7833,10 +7838,10 @@
         <v>117</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -7854,7 +7859,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7872,10 +7877,10 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>374</v>
@@ -7889,10 +7894,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7918,16 +7923,16 @@
         <v>187</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -7955,10 +7960,10 @@
         <v>386</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -7976,7 +7981,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7994,10 +7999,10 @@
         <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>374</v>
@@ -8011,10 +8016,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8037,17 +8042,17 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8096,7 +8101,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8120,7 +8125,7 @@
         <v>83</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8131,10 +8136,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8160,10 +8165,10 @@
         <v>205</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8214,7 +8219,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8235,10 +8240,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8249,10 +8254,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8275,16 +8280,16 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8334,7 +8339,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8355,10 +8360,10 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8369,10 +8374,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8395,16 +8400,16 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8454,7 +8459,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8475,10 +8480,10 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8489,10 +8494,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8515,19 +8520,19 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8576,7 +8581,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8597,10 +8602,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8611,10 +8616,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8729,10 +8734,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8849,14 +8854,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8878,10 +8883,10 @@
         <v>139</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>142</v>
@@ -8936,7 +8941,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8971,10 +8976,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9000,13 +9005,13 @@
         <v>187</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O59" t="s" s="2">
         <v>288</v>
@@ -9037,10 +9042,10 @@
         <v>386</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>83</v>
@@ -9058,7 +9063,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>93</v>
@@ -9076,7 +9081,7 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>292</v>
@@ -9093,10 +9098,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9119,16 +9124,16 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O60" t="s" s="2">
         <v>350</v>
@@ -9180,7 +9185,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9198,7 +9203,7 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>353</v>
@@ -9215,10 +9220,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9244,13 +9249,13 @@
         <v>187</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>359</v>
@@ -9302,7 +9307,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9337,10 +9342,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9366,16 +9371,16 @@
         <v>187</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9424,7 +9429,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9459,10 +9464,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9488,16 +9493,16 @@
         <v>84</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9546,7 +9551,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9567,10 +9572,10 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
@@ -380,7 +380,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -614,7 +614,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -963,7 +963,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1141,7 +1141,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1170,7 +1170,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1225,7 +1225,7 @@
     <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1255,7 +1255,7 @@
     <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1292,7 +1292,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1367,7 +1367,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1417,7 +1417,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1450,7 +1450,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1561,7 +1561,7 @@
     <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR 
--- a/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
@@ -617,7 +617,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>93</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
@@ -1299,7 +1299,7 @@
     <t>このObservationでデータを得るために使われた測定機器に関する情報</t>
   </si>
   <si>
-    <t>これは、結果の送信に関与するデバイス（ゲートウェイなど）を表すことを意図したものではない。そのようなデバイスは、必要に応じてProvenanceリソースを使用して文書化する。</t>
+    <t>これは、結果の送信に関与する機器（ゲートウェイなど）を表すことを意図したものではない。そのような機器は、必要に応じてProvenanceリソースを使用して文書化する。</t>
   </si>
   <si>
     <t>&lt; 49062001 |Device|</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
@@ -645,6 +645,14 @@
     <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS"/&gt;
+    &lt;code value="social-history"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
@@ -799,9 +807,6 @@
   </si>
   <si>
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>social-history</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -3840,7 +3845,7 @@
         <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>83</v>
+        <v>202</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>83</v>
@@ -3859,7 +3864,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -3912,10 +3917,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3938,13 +3943,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3995,7 +4000,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4019,7 +4024,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4030,10 +4035,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4062,7 +4067,7 @@
         <v>140</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>142</v>
@@ -4103,10 +4108,10 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
@@ -4115,7 +4120,7 @@
         <v>194</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4139,7 +4144,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4150,10 +4155,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4176,19 +4181,19 @@
         <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4237,7 +4242,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4258,10 +4263,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4272,10 +4277,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4298,13 +4303,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4355,7 +4360,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4379,7 +4384,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4390,10 +4395,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4422,7 +4427,7 @@
         <v>140</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>142</v>
@@ -4463,10 +4468,10 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
@@ -4475,7 +4480,7 @@
         <v>194</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4499,7 +4504,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4510,10 +4515,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4539,23 +4544,23 @@
         <v>107</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4597,7 +4602,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4618,10 +4623,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4632,10 +4637,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4658,16 +4663,16 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4717,7 +4722,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4738,10 +4743,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4752,10 +4757,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4781,21 +4786,21 @@
         <v>113</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>253</v>
+        <v>83</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -4898,7 +4903,7 @@
         <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>259</v>
@@ -5140,7 +5145,7 @@
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>277</v>
@@ -7202,13 +7207,13 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7259,7 +7264,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7283,7 +7288,7 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7326,7 +7331,7 @@
         <v>140</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>142</v>
@@ -7379,7 +7384,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7403,7 +7408,7 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -8162,7 +8167,7 @@
         <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>466</v>
@@ -8642,13 +8647,13 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8699,7 +8704,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8723,7 +8728,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8766,7 +8771,7 @@
         <v>140</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>142</v>
@@ -8819,7 +8824,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8843,7 +8848,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-socialhistory.xlsx
@@ -540,7 +540,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationStatement_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
 </t>
   </si>
   <si>
@@ -975,7 +975,7 @@
     <t>配偶者、親、胎児、ドナーなど、このObservationのsubject要素が実際の対象でない場合、その実際の対象に関する情報</t>
   </si>
   <si>
-    <t>T通常、observationは対象（患者、または患者のグループ、場所、またはデバイス）について行われ、対象とobservationのために直接測定されるものとの区別は、observationコード自体（例：「血糖値」 ）で記述され、この要素を使用して個別に表す必要はない。検体（標本）への参照が必要な場合は、 `specimen`要素を使用する。リソースの代わりにコードが必要な場合は、人体部位には`bodysite`要素を使用するか、標準の拡張機能[focusCode]（extension-observation-focuscode.html）を使用する。</t>
+    <t>通常、observationは対象（患者、または患者のグループ、場所、またはデバイス）について行われ、対象とobservationのために直接測定されるものとの区別は、observationコード自体（例：「血糖値」 ）で記述され、この要素を使用して個別に表す必要はない。検体（標本）への参照が必要な場合は、 `specimen`要素を使用する。リソースの代わりにコードが必要な場合は、人体部位には`bodysite`要素を使用するか、標準の拡張機能[focusCode]（extension-observation-focuscode.html）を使用する。</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -1533,7 +1533,7 @@
     <t>複数のObservation をグループに一緒にまとめる方法については、以下の[Notes]（observation.html＃notes）を参照すること。</t>
   </si>
   <si>
-    <t>コンポーネントobservation は プライマリobservation としてのobservation リソースの中で同じ属性を共有し、常に単一のobservation の一部として扱われる（つまりそれらは分離可能ではないん）。ただし、プライマリobservationのreference rangeはコンポーネント値に継承されないため、reference rangeは各コンポーネントobservation に適切であれば必要である。</t>
+    <t>コンポーネントobservation は プライマリobservation としてのobservation リソースの中で同じ属性を共有し、常に単一のobservation の一部として扱われる（つまりそれらは分離可能ではない）。ただし、プライマリobservationのreference rangeはコンポーネント値に継承されないため、reference rangeは各コンポーネントobservation に適切であれば必要である。</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
